--- a/currentbuild/StructureDefinition-auditevent-encounter-pointofcare.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-encounter-pointofcare.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:no-basis-auditevent/StructureDefinition/auditevent-encounter-pointofcare</t>
+    <t>http://hl7.no/fhir/StructureDefinition/auditevent-encounter-pointofcare</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-28T16:36:28+00:00</t>
+    <t>2024-06-04T05:44:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,7 +105,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>urn:no-basis-auditevent/StructureDefinition/no-basis-Location</t>
+    <t>http://hl7.no/fhir/StructureDefinition/no-basis-Location</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -767,7 +767,7 @@
     <t>Location.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(urn:no-basis-auditevent/StructureDefinition/auditevent-encounter-pointofcare-organization)
+    <t xml:space="preserve">Reference(http://hl7.no/fhir/StructureDefinition/auditevent-encounter-pointofcare-organization)
 </t>
   </si>
   <si>
@@ -1209,7 +1209,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.53515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="88.6328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/currentbuild/StructureDefinition-auditevent-encounter-pointofcare.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-encounter-pointofcare.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T05:44:14+00:00</t>
+    <t>2024-06-04T06:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-auditevent-encounter-pointofcare.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-encounter-pointofcare.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="287">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T06:11:20+00:00</t>
+    <t>2024-06-06T18:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,7 +250,9 @@
     <t>Details and position information for a physical place</t>
   </si>
   <si>
-    <t>Details and position information for a physical place where services are provided and resources and participants may be stored, found, contained, or accommodated.</t>
+    <t>Details and position information for a physical place where services are provided  and resources and participants may be stored, found, contained or 
+accommodated.
+no-basis: The use-case for no-basis-Location is representation of organization structure to describe where a specific department or healthcare service is offered.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -630,23 +632,27 @@
     <t>Location.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address
+    <t xml:space="preserve">Address {http://hl7.no/fhir/StructureDefinition/no-basis-Address}
 </t>
   </si>
   <si>
-    <t>Physical location</t>
-  </si>
-  <si>
-    <t>Physical location.</t>
-  </si>
-  <si>
-    <t>Additional addresses should be recorded using another instance of the Location resource, or via the Organization.</t>
+    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
+  </si>
+  <si>
+    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
+  </si>
+  <si>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
   </si>
   <si>
     <t>If locations can be visited, we need to keep track of their address.</t>
   </si>
   <si>
-    <t>.addr</t>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>AD</t>
   </si>
   <si>
     <t>Location.physicalType</t>
@@ -892,14 +898,15 @@
     <t>Location.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|http://hl7.no/fhir/StructureDefinition/no-basis-Endpoint)
 </t>
   </si>
   <si>
     <t>Technical endpoints providing access to services operated for the location</t>
   </si>
   <si>
-    <t>Technical endpoints providing access to services operated for the location.</t>
+    <t>no-basis don't use this element to reference endpoints registered in the Norwegian Address register (endpoints connected to a kommunikasjonspart in tjenestebasert adressering). Endpoints registered in the Norwegian Address register should only be referenced through a kommunikasjonspart-Organization resource.
+Technical endpoints providing access to services operated for the location.</t>
   </si>
   <si>
     <t>Organizations may have different systems at different locations that provide various services and need to be able to define the technical connection details for how to connect to them, and for what purpose.</t>
@@ -3390,13 +3397,13 @@
         <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>73</v>
+        <v>203</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>73</v>
@@ -3404,10 +3411,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3433,14 +3440,14 @@
         <v>186</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3465,13 +3472,13 @@
         <v>73</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -3489,7 +3496,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3504,7 +3511,7 @@
         <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>184</v>
@@ -3512,10 +3519,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3538,17 +3545,17 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>73</v>
@@ -3597,7 +3604,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3612,7 +3619,7 @@
         <v>94</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>73</v>
@@ -3620,10 +3627,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3649,10 +3656,10 @@
         <v>162</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3703,7 +3710,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3726,10 +3733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3758,7 +3765,7 @@
         <v>129</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>131</v>
@@ -3811,7 +3818,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3834,14 +3841,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3863,10 +3870,10 @@
         <v>128</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>131</v>
@@ -3921,7 +3928,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3944,10 +3951,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3970,13 +3977,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4027,7 +4034,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -4042,7 +4049,7 @@
         <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>73</v>
@@ -4050,10 +4057,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4076,13 +4083,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4133,7 +4140,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -4148,7 +4155,7 @@
         <v>94</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>73</v>
@@ -4156,10 +4163,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4182,13 +4189,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4239,7 +4246,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4254,7 +4261,7 @@
         <v>94</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>73</v>
@@ -4262,10 +4269,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4288,19 +4295,19 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>73</v>
@@ -4349,7 +4356,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4364,7 +4371,7 @@
         <v>94</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>73</v>
@@ -4372,10 +4379,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4398,17 +4405,17 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>73</v>
@@ -4457,7 +4464,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4472,7 +4479,7 @@
         <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>73</v>
@@ -4480,10 +4487,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4506,16 +4513,16 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4565,7 +4572,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4580,7 +4587,7 @@
         <v>94</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>73</v>
@@ -4588,10 +4595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4617,10 +4624,10 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4671,7 +4678,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4694,10 +4701,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4726,7 +4733,7 @@
         <v>129</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>131</v>
@@ -4779,7 +4786,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4802,14 +4809,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4831,10 +4838,10 @@
         <v>128</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>131</v>
@@ -4889,7 +4896,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4912,10 +4919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4941,10 +4948,10 @@
         <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4974,10 +4981,10 @@
         <v>149</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>73</v>
@@ -4995,7 +5002,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5010,7 +5017,7 @@
         <v>94</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>73</v>
@@ -5018,10 +5025,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5044,13 +5051,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5101,7 +5108,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -5116,7 +5123,7 @@
         <v>94</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
@@ -5124,10 +5131,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5150,13 +5157,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5207,7 +5214,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5222,7 +5229,7 @@
         <v>94</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>73</v>
@@ -5230,10 +5237,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5256,13 +5263,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5313,7 +5320,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5328,7 +5335,7 @@
         <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>73</v>
@@ -5336,10 +5343,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5365,10 +5372,10 @@
         <v>162</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5419,7 +5426,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5442,10 +5449,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5468,17 +5475,17 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>73</v>
@@ -5527,7 +5534,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
